--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -6733,20 +6733,30 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>279</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DL-01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Public hostnames and DNS provider</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Subdomains of quack.ryt.dev; DNS-only CNAMEs in Cloudflare; no Route 53</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-001-hostnames-and-dns.md</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -6760,39 +6760,139 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>DL-02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-002-compute.md</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DL-03</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ECS capacity provider</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Fargate</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-003-capacity-provider.md</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>DL-04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>HTTP and WebSocket entry point</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>One Application Load Balancer for both; no API Gateway</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-004-http-entry-point.md</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>DL-05</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Fan-out between tasks</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Valkey pub/sub on ElastiCache</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-005-fan-out-between-tasks.md</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DL-06</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ID token verification</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>In code for HTTP and WebSockets</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-006-token-verification.md</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -6895,11 +6895,31 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DL-07</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Repository and stack layout</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Monorepo; one CDK stack per deployable; one ECS service per HTTP domain; no CloudFormation exports</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-007-stack-layout.md</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -6922,11 +6922,31 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DL-08</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Cross-domain reads</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Direct read of another domain's records under a stated rule; no service-to-service calls in the MVP</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-008-cross-domain-reads.md</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -487,7 +487,7 @@
     <t>Does access need role based access control (RBAC), record level access, or both?</t>
   </si>
   <si>
-    <t>Is this multi tenant, and how strict must tenant isolation be?</t>
+    <t>Is this multi pond, and how strict must pond isolation be?</t>
   </si>
   <si>
     <t>What must be auditable, and who consumes the audit trail?</t>
@@ -1238,10 +1238,10 @@
     <t>OOS-09</t>
   </si>
   <si>
-    <t>Multi-tenancy</t>
-  </si>
-  <si>
-    <t>Single tenant required; tenant key kept in the data model</t>
+    <t>Multiple ponds</t>
+  </si>
+  <si>
+    <t>Single pond required; pond key kept in the data model</t>
   </si>
   <si>
     <t>Named future enhancement</t>
@@ -1421,7 +1421,7 @@
     <t>OOS-11</t>
   </si>
   <si>
-    <t>No compliance program (GDPR, CCPA, SOC 2); owner and member roles only, no admin role; request logs only, no exportable audit log. Tenancy is OOS-09.</t>
+    <t>No compliance program (GDPR, CCPA, SOC 2); owner and member roles only, no admin role; request logs only, no exportable audit log. Ponds are OOS-09.</t>
   </si>
   <si>
     <t>GDPR and CCPA; SOC 2 Type II as the control framework. Privacy Operations owner TBD*</t>
@@ -1433,10 +1433,10 @@
     <t>Record level. Flock membership for read and write; ownership for delete.</t>
   </si>
   <si>
-    <t>Multi-tenant with strict isolation: every query scoped by tenant.*</t>
-  </si>
-  <si>
-    <t>Single tenant in demo, but with data model shaped to include tenancy. See OOS-09.</t>
+    <t>Multi-pond with strict isolation: every query scoped by pond.*</t>
+  </si>
+  <si>
+    <t>Single pond in demo, but with data model shaped to include ponds. See OOS-09.</t>
   </si>
   <si>
     <t xml:space="preserve">Sign-ins, flock create and delete, and member additions. Non-deleted message history only. Compliance officers TBD. </t>
@@ -1622,10 +1622,10 @@
     <t>NFR-11</t>
   </si>
   <si>
-    <t>Record-level tenant isolation</t>
-  </si>
-  <si>
-    <t>Every record carries the tenant key. One hardcoded tenant is used.</t>
+    <t>Record-level pond isolation</t>
+  </si>
+  <si>
+    <t>Every record carries the pond key. One hardcoded pond is used.</t>
   </si>
   <si>
     <t>OOS-09; FC-01</t>
@@ -1634,10 +1634,10 @@
     <t>12 to 24 months</t>
   </si>
   <si>
-    <t>Key rewrite and data migration if the tenant key is absent from any key</t>
-  </si>
-  <si>
-    <t>Tenant key in every key now; nothing else built</t>
+    <t>Key rewrite and data migration if the pond key is absent from any key</t>
+  </si>
+  <si>
+    <t>Pond key in every key now; nothing else built</t>
   </si>
   <si>
     <t>FC-02</t>
@@ -1709,7 +1709,7 @@
     <t>A person who has signed in</t>
   </si>
   <si>
-    <t>tenantId, duckId, googleSubject, email, displayName, createdAt</t>
+    <t>pondId, duckId, googleSubject, email, displayName, createdAt</t>
   </si>
   <si>
     <t>Identity copied from the Google ID token at sign-in</t>
@@ -1724,7 +1724,7 @@
     <t>A named channel</t>
   </si>
   <si>
-    <t>tenantId, flockId, name, ownerId, createdAt</t>
+    <t>pondId, flockId, name, ownerId, createdAt</t>
   </si>
   <si>
     <t>ownerId is the creator; ownership is not transferable</t>
@@ -1739,7 +1739,7 @@
     <t>A user belongs to a flock</t>
   </si>
   <si>
-    <t>tenantId, flockId, duckId, addedBy, addedAt</t>
+    <t>pondId, flockId, duckId, addedBy, addedAt</t>
   </si>
   <si>
     <t>DE-04</t>
@@ -1751,7 +1751,7 @@
     <t>One text message in a flock</t>
   </si>
   <si>
-    <t>tenantId, flockId, messageId (time ordered), senderId (duckId), text, createdAt</t>
+    <t>pondId, flockId, messageId (time ordered), senderId (duckId), text, createdAt</t>
   </si>
   <si>
     <t>text at most 4,000 characters (ASM-03); item stays under the 400 KB limit (NFR-10)</t>
@@ -1766,7 +1766,7 @@
     <t>A live session for one user</t>
   </si>
   <si>
-    <t>tenantId, connectionId, duckId, createdAt</t>
+    <t>pondId, connectionId, duckId, createdAt</t>
   </si>
   <si>
     <t>Data Access Patterns</t>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Scale and Estimates" sheetId="4" r:id="rId5"/>
     <sheet name="Decision Log" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="681">
   <si>
     <t>Date Created</t>
   </si>
@@ -1613,10 +1613,10 @@
     <t>Platform standard</t>
   </si>
   <si>
-    <t>A message item stays under the 400 KB item limit</t>
-  </si>
-  <si>
-    <t>https://docs.aws.amazon.com/amazondynamodb/latest/developerguide/Constraints.html</t>
+    <t>A message record stays under 400 KB</t>
+  </si>
+  <si>
+    <t>Service target. The data store ADR confirms the chosen store's record limit meets it.</t>
   </si>
   <si>
     <t>NFR-11</t>
@@ -1697,7 +1697,7 @@
     <t>If the demo outlives one month or the RPO must hold for code and operator error</t>
   </si>
   <si>
-    <t>DynamoDB Streams to a durable sink such as S3 through Firehose; after a restore, replay the gap. Keep the write path behind one module so the stream can be added without touching handlers. https://docs.aws.amazon.com/amazondynamodb/latest/developerguide/PointInTimeRecovery_Howitworks.html</t>
+    <t>A change stream from the data store to a durable sink such as S3; after a restore, replay the gap. Keep the write path behind one module so the stream can be added without touching handlers.</t>
   </si>
   <si>
     <t>Data Entities</t>
@@ -1754,7 +1754,7 @@
     <t>pondId, flockId, messageId (time ordered), senderId (duckId), text, createdAt</t>
   </si>
   <si>
-    <t>text at most 4,000 characters (ASM-03); item stays under the 400 KB limit (NFR-10)</t>
+    <t>text at most 4,000 characters (ASM-03); record stays under 400 KB (NFR-10)</t>
   </si>
   <si>
     <t>DE-05</t>
@@ -1880,10 +1880,10 @@
     <t>Put on connect; delete on disconnect</t>
   </si>
   <si>
-    <t>1,700 per second at steady state</t>
-  </si>
-  <si>
-    <t>12,000,000 users divided by the 7,200 second connection cap; higher at start of day. https://docs.aws.amazon.com/apigateway/latest/developerguide/apigateway-execution-service-websocket-limits-table.html</t>
+    <t>2,500 per second at peak</t>
+  </si>
+  <si>
+    <t>A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour; sourced in the sign-in design). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
   </si>
   <si>
     <t>AP-15</t>
@@ -1955,7 +1955,7 @@
     <t>Assumption: message text plus keys and attributes.</t>
   </si>
   <si>
-    <t>Assumption: table plus point-in-time recovery copy. Replicas across availability zones are not billed separately (https://aws.amazon.com/dynamodb/pricing/on-demand/).</t>
+    <t>Assumption: primary plus one backup copy</t>
   </si>
   <si>
     <t>Assumption: only recent messages are read. Entered as a fraction because the formula multiplies directly.</t>
@@ -2070,6 +2070,24 @@
   </si>
   <si>
     <t xml:space="preserve">*See OOS-10 caveat on point-in-time recovery. </t>
+  </si>
+  <si>
+    <t>Not stored. Sockets live in websocket task memory; live delivery goes through the per-flock fan-out topic (ADR-005). See AP-14 and AP-15.</t>
+  </si>
+  <si>
+    <t>Connect; disconnect (held in task memory)</t>
+  </si>
+  <si>
+    <t>Not a data store access pattern; sizes the websocket service. A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour; sourced in the sign-in design). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
+  </si>
+  <si>
+    <t>Find the connections of a flock's members</t>
+  </si>
+  <si>
+    <t>Not a data store access pattern. One publish per send to the flock's fan-out topic; each subscribed task pushes to its own sockets (ADR-005).</t>
+  </si>
+  <si>
+    <t>Assumption: membership check plus one put. Fan-out uses the pub/sub topic, not a data store lookup (ADR-005).</t>
   </si>
 </sst>
 </file>
@@ -5542,7 +5560,9 @@
       <c r="D8" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -5892,13 +5912,13 @@
         <v>570</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>610</v>
+        <v>676</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>611</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>612</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -5909,13 +5929,13 @@
         <v>570</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>614</v>
+        <v>678</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>670</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>615</v>
+        <v>679</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6100,13 +6120,13 @@
         <v>200</v>
       </c>
       <c r="C10" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>629</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -6518,7 +6538,7 @@
       </c>
       <c r="C39" s="21">
         <f>IF(COUNT($C$37,$C$10)&lt;2,"Missing Info",$C$37*$C$10)</f>
-        <v>11666.666666666666</v>
+        <v>7777.7777777777774</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>249</v>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="685">
   <si>
     <t>Date Created</t>
   </si>
@@ -2088,6 +2088,18 @@
   </si>
   <si>
     <t>Assumption: membership check plus one put. Fan-out uses the pub/sub topic, not a data store lookup (ADR-005).</t>
+  </si>
+  <si>
+    <t>User identity (Google subject, display name) is copied from the Google ID token at sign-in. Email is read from the token and not stored.</t>
+  </si>
+  <si>
+    <t>Personal data: Google subject, display name. Message text is user content. Classified external; no explicit payment, health, or regulated data requested by product.</t>
+  </si>
+  <si>
+    <t>Only Google subject and display name are held</t>
+  </si>
+  <si>
+    <t>pondId, duckId, googleSubject, displayName (unique per pond), createdAt</t>
   </si>
 </sst>
 </file>
@@ -4574,7 +4586,7 @@
         <v>142</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>453</v>
+        <v>681</v>
       </c>
       <c r="C27" s="2"/>
     </row>
@@ -4592,7 +4604,7 @@
         <v>144</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>455</v>
+        <v>682</v>
       </c>
       <c r="C29" s="2"/>
     </row>
@@ -5103,7 +5115,7 @@
         <v>505</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>512</v>
+        <v>683</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>348</v>
@@ -5492,7 +5504,7 @@
         <v>553</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>554</v>
+        <v>684</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>555</v>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -1883,7 +1883,7 @@
     <t>2,500 per second at peak</t>
   </si>
   <si>
-    <t>A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour; sourced in the sign-in design). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
+    <t>A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
   </si>
   <si>
     <t>AP-15</t>
@@ -2078,7 +2078,7 @@
     <t>Connect; disconnect (held in task memory)</t>
   </si>
   <si>
-    <t>Not a data store access pattern; sizes the websocket service. A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour; sourced in the sign-in design). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
+    <t>Not a data store access pattern; sizes the websocket service. A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
   </si>
   <si>
     <t>Find the connections of a flock's members</t>
@@ -5951,11 +5951,31 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AP-16</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DE-01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>List ducks in the pond</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>14 per second at peak</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>One per add member: the client loads the list to pick the duck</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\joe\quack\docs\discovery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0884A0D0-C673-45F1-A31E-DC7B4C011127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F9B9A0-0101-44CA-B34C-7376DE4A0750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25470" yWindow="0" windowWidth="25800" windowHeight="20880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="720" windowWidth="25800" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Brief" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Scale and Estimates" sheetId="4" r:id="rId5"/>
     <sheet name="Decision Log" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="718">
   <si>
     <t>Date Created</t>
   </si>
@@ -868,18 +868,6 @@
     <t>DL-01</t>
   </si>
   <si>
-    <t>Event transport between order service and fulfillment</t>
-  </si>
-  <si>
-    <t>EventBridge</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>docs/adr/ADR-004-event-transport.md</t>
-  </si>
-  <si>
     <t>Joe Martin</t>
   </si>
   <si>
@@ -905,9 +893,6 @@
   </si>
   <si>
     <t>Position</t>
-  </si>
-  <si>
-    <t>TBD</t>
   </si>
   <si>
     <t>VP of Engineering</t>
@@ -1311,12 +1296,6 @@
   </si>
   <si>
     <t>Daisy Duck</t>
-  </si>
-  <si>
-    <t>Priced in Phase 2 once the architecture is chosen; Scale sheet supplies the volumes. Filled in Step 4</t>
-  </si>
-  <si>
-    <t>Priced in Phase 2 once the architecture is chosen</t>
   </si>
   <si>
     <t>OOS-10</t>
@@ -1406,15 +1385,9 @@
     <t>Users as known to this service, flocks, memberships, messages, and live connections.</t>
   </si>
   <si>
-    <t>User identity (Google subject, email, display name) is copied from the Google ID token at sign-in.</t>
-  </si>
-  <si>
     <t>Deleting a flock deletes its messages and memberships. Live connection records are removed on disconnect. Nothing else is deleted.</t>
   </si>
   <si>
-    <t>Personal data: Google subject, email, display name. Message text is user content. Classified external; no explicit payment, health, or regulated data requested by product.</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -1583,9 +1556,6 @@
     <t>No credentials are stored.</t>
   </si>
   <si>
-    <t>Only Google subject, email, and display name are held</t>
-  </si>
-  <si>
     <t>NFR-08</t>
   </si>
   <si>
@@ -1709,9 +1679,6 @@
     <t>A person who has signed in</t>
   </si>
   <si>
-    <t>pondId, duckId, googleSubject, email, displayName, createdAt</t>
-  </si>
-  <si>
     <t>Identity copied from the Google ID token at sign-in</t>
   </si>
   <si>
@@ -1877,24 +1844,12 @@
     <t>AP-14</t>
   </si>
   <si>
-    <t>Put on connect; delete on disconnect</t>
-  </si>
-  <si>
     <t>2,500 per second at peak</t>
   </si>
   <si>
-    <t>A socket lives one ID token lifetime, then the client reconnects (Assumption: 1 hour). Daily active users x 9 connected hours / 1 hour / 86,400 seconds is 1,250 per second average; x2 peak ratio. Higher at start of day.</t>
-  </si>
-  <si>
     <t>AP-15</t>
   </si>
   <si>
-    <t>List connections for a set of users</t>
-  </si>
-  <si>
-    <t>One per send; feeds deliveries: sends times connected recipients</t>
-  </si>
-  <si>
     <t>280 per second at peak</t>
   </si>
   <si>
@@ -1934,9 +1889,6 @@
     <t>Assumption: membership check plus one query.</t>
   </si>
   <si>
-    <t>Assumption: membership check, one put, one connection lookup for fan-out.</t>
-  </si>
-  <si>
     <t>Derived: share of users connected at peak (0.7, row 22) divided by the average share connected (9 of 24 hours, 0.375) is 1.87, rounded up. Users are global, so a day of traffic spreads across the clock.</t>
   </si>
   <si>
@@ -2100,6 +2052,153 @@
   </si>
   <si>
     <t>pondId, duckId, googleSubject, displayName (unique per pond), createdAt</t>
+  </si>
+  <si>
+    <t>At scale: about $46,000 per month over 21.6 billion HTTP requests, from the cost table in docs/design/operational-design.md.</t>
+  </si>
+  <si>
+    <t>Cost table in docs/design/operational-design.md: about $150 per month for the demo, about $46,000 per month at scale, times 12.</t>
+  </si>
+  <si>
+    <t>AP-16</t>
+  </si>
+  <si>
+    <t>List ducks in the pond</t>
+  </si>
+  <si>
+    <t>One per add member: the client loads the list to pick the duck</t>
+  </si>
+  <si>
+    <t>Sockets per websocket task</t>
+  </si>
+  <si>
+    <t>Open WebSocket connections one task holds before scaling out.</t>
+  </si>
+  <si>
+    <t>Assumption: memory bound, single-digit kilobytes per idle socket in Node. Verified by the Phase 3 load test. Cited by ADR-005.</t>
+  </si>
+  <si>
+    <t>Public hostnames and DNS provider</t>
+  </si>
+  <si>
+    <t>Subdomains of quack.ryt.dev; DNS-only CNAMEs in Cloudflare; no Route 53</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-001-hostnames-and-dns.md</t>
+  </si>
+  <si>
+    <t>DL-02</t>
+  </si>
+  <si>
+    <t>Compute</t>
+  </si>
+  <si>
+    <t>ECS</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-002-compute.md</t>
+  </si>
+  <si>
+    <t>DL-03</t>
+  </si>
+  <si>
+    <t>ECS capacity provider</t>
+  </si>
+  <si>
+    <t>Fargate</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-003-capacity-provider.md</t>
+  </si>
+  <si>
+    <t>DL-04</t>
+  </si>
+  <si>
+    <t>HTTP and WebSocket entry point</t>
+  </si>
+  <si>
+    <t>One Application Load Balancer for both; no API Gateway</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-004-http-entry-point.md</t>
+  </si>
+  <si>
+    <t>DL-05</t>
+  </si>
+  <si>
+    <t>Fan-out between tasks</t>
+  </si>
+  <si>
+    <t>Valkey pub/sub on ElastiCache</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-005-fan-out-between-tasks.md</t>
+  </si>
+  <si>
+    <t>DL-06</t>
+  </si>
+  <si>
+    <t>ID token verification</t>
+  </si>
+  <si>
+    <t>In code for HTTP and WebSockets</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-006-token-verification.md</t>
+  </si>
+  <si>
+    <t>DL-07</t>
+  </si>
+  <si>
+    <t>Repository and stack layout</t>
+  </si>
+  <si>
+    <t>Monorepo; one CDK stack per deployable; one ECS service per HTTP domain; no CloudFormation exports</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-007-stack-layout.md</t>
+  </si>
+  <si>
+    <t>DL-08</t>
+  </si>
+  <si>
+    <t>Cross-domain reads</t>
+  </si>
+  <si>
+    <t>Direct read of another domain's records under a stated rule; no service-to-service calls in the MVP</t>
+  </si>
+  <si>
+    <t>docs/adr/adr-008-cross-domain-reads.md</t>
+  </si>
+  <si>
+    <t>The demo runs one month (Scoping Q40). $1,800 at demo load;</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-01-sign-in.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-02-create-flock.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-03-list-flocks.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-04-add-member.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-05-send-message.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-06-load-history.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-07-connect-and-disconnect.md</t>
+  </si>
+  <si>
+    <t>docs/design/flows/wfl-08-delete-flock.md</t>
   </si>
 </sst>
 </file>
@@ -2182,7 +2281,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2197,12 +2296,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2255,7 +2348,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2278,22 +2371,13 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2303,9 +2387,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2323,26 +2404,32 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2351,6 +2438,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2673,98 +2763,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="23" t="s">
+      <c r="D1" s="28"/>
+      <c r="E1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="24"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="23">
         <v>46276</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="30">
+      <c r="B2" s="24"/>
+      <c r="C2" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="23">
         <v>46276</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="26" t="s">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="28" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
     </row>
     <row r="6" spans="1:10" ht="95.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
+      <c r="A6" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2777,7 +2867,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>12</v>
@@ -2788,58 +2878,58 @@
         <v>13</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E14" s="6"/>
     </row>
@@ -2858,24 +2948,24 @@
       <c r="E16" s="2"/>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2899,45 +2989,45 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E23" s="2"/>
     </row>
@@ -2963,24 +3053,24 @@
       <c r="E26" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -3007,162 +3097,162 @@
         <v>26</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>289</v>
+      <c r="E31" s="33" t="s">
+        <v>710</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>289</v>
+      <c r="E32" s="33" t="s">
+        <v>711</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>289</v>
+      <c r="E33" s="33" t="s">
+        <v>712</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>289</v>
+      <c r="E34" s="33" t="s">
+        <v>713</v>
       </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>289</v>
+      <c r="E35" s="33" t="s">
+        <v>714</v>
       </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>289</v>
+      <c r="E36" s="33" t="s">
+        <v>715</v>
       </c>
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>289</v>
+      <c r="E37" s="33" t="s">
+        <v>716</v>
       </c>
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>289</v>
+      <c r="E38" s="33" t="s">
+        <v>717</v>
       </c>
       <c r="F38" s="2"/>
     </row>
     <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -3189,10 +3279,10 @@
         <v>33</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -3204,10 +3294,10 @@
         <v>35</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -3220,10 +3310,10 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3234,10 +3324,10 @@
         <v>39</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E46" s="2"/>
     </row>
@@ -3249,10 +3339,10 @@
         <v>41</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>280</v>
+        <v>326</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="E47" s="2"/>
     </row>
@@ -3271,34 +3361,34 @@
       <c r="E49" s="2"/>
     </row>
     <row r="51" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
     </row>
     <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-    </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>9</v>
       </c>
@@ -3335,31 +3425,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I54" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D54" s="6" t="s">
+      <c r="J54" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3423,22 +3513,22 @@
       <c r="J59" s="2"/>
     </row>
     <row r="61" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
     </row>
     <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28" t="s">
+      <c r="A62" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
@@ -3467,7 +3557,7 @@
       <c r="C64" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="14">
+      <c r="D64" s="11">
         <v>500</v>
       </c>
       <c r="E64" s="6"/>
@@ -3482,7 +3572,7 @@
       <c r="C65" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="14">
+      <c r="D65" s="11">
         <v>1000</v>
       </c>
       <c r="E65" s="6"/>
@@ -3497,7 +3587,7 @@
       <c r="C66" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D66" s="14">
+      <c r="D66" s="11">
         <v>2000</v>
       </c>
       <c r="E66" s="6"/>
@@ -3512,11 +3602,11 @@
       <c r="C67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="15">
+      <c r="D67" s="12">
         <v>0.999</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3529,11 +3619,11 @@
       <c r="C68" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>340</v>
+      <c r="D68" s="10" t="s">
+        <v>335</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3546,7 +3636,7 @@
       <c r="C69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="18">
         <v>16667</v>
       </c>
       <c r="E69" s="6"/>
@@ -3561,11 +3651,11 @@
       <c r="C70" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="13">
         <v>1</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,11 +3668,11 @@
       <c r="C71" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="13">
         <v>60</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -3595,11 +3685,11 @@
       <c r="C72" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D72" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>424</v>
+      <c r="D72" s="19">
+        <v>2E-3</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,22 +3721,22 @@
       <c r="E76" s="2"/>
     </row>
     <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="26" t="s">
+      <c r="A78" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
+      <c r="A79" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
@@ -3670,87 +3760,87 @@
         <v>87</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E83" s="6"/>
     </row>
     <row r="84" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>42</v>
@@ -3779,22 +3869,22 @@
       <c r="E89" s="2"/>
     </row>
     <row r="91" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="26" t="s">
+      <c r="A91" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
+      <c r="A92" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
@@ -3821,10 +3911,10 @@
         <v>94</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E94" s="2"/>
     </row>
@@ -3835,11 +3925,11 @@
       <c r="B95" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="9">
         <v>0</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E95" s="6"/>
     </row>
@@ -3850,27 +3940,29 @@
       <c r="B96" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="9">
         <v>0</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E96" s="2"/>
     </row>
-    <row r="97" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="57" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C97" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11" t="s">
-        <v>425</v>
+      <c r="C97" s="20">
+        <v>550000</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3888,22 +3980,22 @@
       <c r="E99" s="2"/>
     </row>
     <row r="101" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="26" t="s">
+      <c r="A101" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="27"/>
-      <c r="C101" s="27"/>
-      <c r="D101" s="27"/>
-      <c r="E101" s="27"/>
+      <c r="B101" s="22"/>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="28" t="s">
+      <c r="A102" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
-      <c r="E102" s="29"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
@@ -3927,43 +4019,43 @@
         <v>105</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E106" s="2"/>
     </row>
@@ -3989,22 +4081,22 @@
       <c r="E109" s="2"/>
     </row>
     <row r="111" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27"/>
-      <c r="D111" s="27"/>
-      <c r="E111" s="27"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="28" t="s">
+      <c r="A112" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="26"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
@@ -4028,168 +4120,168 @@
         <v>111</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E116" s="2"/>
     </row>
     <row r="117" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4200,24 +4292,24 @@
       <c r="E125" s="2"/>
     </row>
     <row r="127" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="26" t="s">
+      <c r="A127" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="B127" s="27"/>
-      <c r="C127" s="27"/>
-      <c r="D127" s="27"/>
-      <c r="E127" s="27"/>
-      <c r="F127" s="27"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
     </row>
     <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="28" t="s">
+      <c r="A128" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="B128" s="29"/>
-      <c r="C128" s="29"/>
-      <c r="D128" s="29"/>
-      <c r="E128" s="29"/>
-      <c r="F128" s="29"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
@@ -4244,30 +4336,30 @@
         <v>118</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>177</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>177</v>
@@ -4276,18 +4368,18 @@
         <v>177</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>416</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>177</v>
@@ -4296,27 +4388,27 @@
         <v>177</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4345,10 +4437,6 @@
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F6:J6"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A52:J52"/>
@@ -4363,6 +4451,10 @@
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F6:J6"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4400,10 +4492,10 @@
         <v>122</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4416,10 +4508,10 @@
         <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="71.25" x14ac:dyDescent="0.25">
@@ -4427,10 +4519,10 @@
         <v>125</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="57" x14ac:dyDescent="0.25">
@@ -4438,10 +4530,10 @@
         <v>126</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
@@ -4449,10 +4541,10 @@
         <v>127</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="57" x14ac:dyDescent="0.25">
@@ -4460,10 +4552,10 @@
         <v>128</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4476,7 +4568,7 @@
         <v>130</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -4485,7 +4577,7 @@
         <v>131</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -4494,7 +4586,7 @@
         <v>132</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C15" s="2"/>
     </row>
@@ -4508,10 +4600,10 @@
         <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
@@ -4519,10 +4611,10 @@
         <v>135</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,10 +4622,10 @@
         <v>136</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4541,10 +4633,10 @@
         <v>137</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="71.25" x14ac:dyDescent="0.25">
@@ -4552,7 +4644,7 @@
         <v>138</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -4561,10 +4653,10 @@
         <v>139</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4577,7 +4669,7 @@
         <v>141</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="C26" s="2"/>
     </row>
@@ -4586,7 +4678,7 @@
         <v>142</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="C27" s="2"/>
     </row>
@@ -4595,7 +4687,7 @@
         <v>143</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C28" s="2"/>
     </row>
@@ -4604,7 +4696,7 @@
         <v>144</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="C29" s="2"/>
     </row>
@@ -4613,7 +4705,7 @@
         <v>145</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C30" s="2"/>
     </row>
@@ -4627,10 +4719,10 @@
         <v>147</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
@@ -4638,7 +4730,7 @@
         <v>148</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C34" s="2"/>
     </row>
@@ -4647,10 +4739,10 @@
         <v>149</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
@@ -4658,10 +4750,10 @@
         <v>150</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -4674,16 +4766,16 @@
         <v>152</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="C39" s="11"/>
+        <v>650</v>
+      </c>
+      <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C40" s="2"/>
     </row>
@@ -4692,7 +4784,7 @@
         <v>154</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C41" s="2"/>
     </row>
@@ -4756,20 +4848,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -4790,7 +4882,7 @@
         <v>158</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>159</v>
@@ -4801,128 +4893,128 @@
     </row>
     <row r="5" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4968,22 +5060,22 @@
       <c r="D20" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -5007,30 +5099,30 @@
         <v>163</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>75</v>
@@ -5038,33 +5130,33 @@
     </row>
     <row r="27" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>72</v>
@@ -5072,33 +5164,33 @@
     </row>
     <row r="29" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>53</v>
@@ -5106,87 +5198,87 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -5218,24 +5310,24 @@
       <c r="E39" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -5262,119 +5354,119 @@
         <v>176</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,22 +5551,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>551</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>552</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="A2" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -5498,82 +5590,82 @@
         <v>170</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5661,29 +5753,29 @@
       <c r="E20" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>574</v>
-      </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="A22" s="32" t="s">
+        <v>563</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>168</v>
@@ -5697,284 +5789,274 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>620</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="57" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>AP-16</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>DE-01</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>List ducks in the pond</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>14 per second at peak</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>One per add member: the client loads the list to pick the duck</t>
-        </is>
+      <c r="A40" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6008,22 +6090,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -6049,14 +6131,14 @@
       <c r="B4" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="15">
         <v>12000000</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
@@ -6066,14 +6148,14 @@
       <c r="B5" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="15">
         <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
@@ -6083,14 +6165,14 @@
       <c r="B6" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="15">
         <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>188</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6100,14 +6182,14 @@
       <c r="B7" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="15">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -6117,14 +6199,14 @@
       <c r="B8" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="15">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6134,14 +6216,14 @@
       <c r="B9" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="15">
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>628</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6151,14 +6233,14 @@
       <c r="B10" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="15">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>198</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -6168,14 +6250,14 @@
       <c r="B11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="15">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>203</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -6185,14 +6267,14 @@
       <c r="B12" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="15">
         <v>0.2</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6202,14 +6284,14 @@
       <c r="B13" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="15">
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -6219,14 +6301,14 @@
       <c r="B14" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="15">
         <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6236,14 +6318,14 @@
       <c r="B15" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="15">
         <v>850</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6253,14 +6335,14 @@
       <c r="B16" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="14">
         <v>0.3</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>206</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6270,14 +6352,14 @@
       <c r="B17" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="15">
         <v>730</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>217</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -6287,14 +6369,14 @@
       <c r="B18" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="15">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>203</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
@@ -6304,73 +6386,83 @@
       <c r="B19" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="15">
         <v>0.05</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>222</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="C20" s="19">
+        <v>623</v>
+      </c>
+      <c r="C20" s="15">
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="C21" s="19">
+        <v>627</v>
+      </c>
+      <c r="C21" s="15">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C22" s="19">
+        <v>631</v>
+      </c>
+      <c r="C22" s="15">
         <v>0.7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C23" s="15">
+        <v>50000</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
@@ -6401,22 +6493,22 @@
       <c r="E27" s="2"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -6442,7 +6534,7 @@
       <c r="B32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="17">
         <f>IF(COUNT($C$4,$C$5,$C$7)&lt;3,"Missing Info",$C$4*$C$5*$C$7)</f>
         <v>552000000</v>
       </c>
@@ -6460,7 +6552,7 @@
       <c r="B33" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="17">
         <f>IF(COUNT($C$4,$C$6,$C$8)&lt;3,"Missing Info",$C$4*$C$6*$C$8)</f>
         <v>168000000</v>
       </c>
@@ -6478,7 +6570,7 @@
       <c r="B34" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="17">
         <f>IF(COUNT($C$32)&lt;1,"Missing Info",$C$32/86400)</f>
         <v>6388.8888888888887</v>
       </c>
@@ -6496,7 +6588,7 @@
       <c r="B35" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="17">
         <f>IF(COUNT($C$33)&lt;1,"Missing Info",$C$33/86400)</f>
         <v>1944.4444444444443</v>
       </c>
@@ -6514,7 +6606,7 @@
       <c r="B36" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="17">
         <f>IF(COUNT($C$34,$C$11)&lt;2,"Missing Info",$C$34*$C$11)</f>
         <v>12777.777777777777</v>
       </c>
@@ -6532,7 +6624,7 @@
       <c r="B37" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="17">
         <f>IF(COUNT($C$35,$C$11)&lt;2,"Missing Info",$C$35*$C$11)</f>
         <v>3888.8888888888887</v>
       </c>
@@ -6550,7 +6642,7 @@
       <c r="B38" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="17">
         <f>IF(COUNT($C$36,$C$9)&lt;2,"Missing Info",$C$36*$C$9)</f>
         <v>25555.555555555555</v>
       </c>
@@ -6568,7 +6660,7 @@
       <c r="B39" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="17">
         <f>IF(COUNT($C$37,$C$10)&lt;2,"Missing Info",$C$37*$C$10)</f>
         <v>7777.7777777777774</v>
       </c>
@@ -6586,7 +6678,7 @@
       <c r="B40" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="16">
         <f>IF(COUNT($C$4,$C$6,$C$16)&lt;3,"Missing Info",$C$4*$C$6*$C$16/1048576)</f>
         <v>48.065185546875</v>
       </c>
@@ -6604,7 +6696,7 @@
       <c r="B41" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="17">
         <f>IF(COUNT($C$40)&lt;1,"Missing Info",$C$40*365)</f>
         <v>17543.792724609375</v>
       </c>
@@ -6622,7 +6714,7 @@
       <c r="B42" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="17">
         <f>IF(COUNT($C$40,$C$17,$C$18)&lt;3,"Missing Info",$C$40*$C$17*$C$18)</f>
         <v>70175.1708984375</v>
       </c>
@@ -6640,7 +6732,7 @@
       <c r="B43" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="17">
         <f>IF(COUNT($C$42,$C$19)&lt;2,"Missing Info",$C$42*$C$19)</f>
         <v>3508.758544921875</v>
       </c>
@@ -6653,56 +6745,56 @@
     </row>
     <row r="44" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="C44" s="21">
+        <v>635</v>
+      </c>
+      <c r="C44" s="17">
         <f>IF(COUNT($C$37,$C$20)&lt;2,"Missing Info",$C$37*$C$20)</f>
         <v>38888.888888888891</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="C45" s="21">
+        <v>639</v>
+      </c>
+      <c r="C45" s="17">
         <f>IF(COUNT($C$4,$C$21)&lt;2,"Missing Info",$C$4*$C$21/24)</f>
         <v>4500000</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="C46" s="21">
+        <v>643</v>
+      </c>
+      <c r="C46" s="17">
         <f>IF(COUNT($C$4,$C$22)&lt;2,"Missing Info",$C$4*$C$22)</f>
         <v>8400000</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6750,22 +6842,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -6785,219 +6877,139 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>DL-01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Public hostnames and DNS provider</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Subdomains of quack.ryt.dev; DNS-only CNAMEs in Cloudflare; no Route 53</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-001-hostnames-and-dns.md</t>
-        </is>
+      <c r="A4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>DL-02</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Compute</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-002-compute.md</t>
-        </is>
+      <c r="A5" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>DL-03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ECS capacity provider</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Fargate</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-003-capacity-provider.md</t>
-        </is>
+      <c r="A6" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>DL-04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>HTTP and WebSocket entry point</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>One Application Load Balancer for both; no API Gateway</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-004-http-entry-point.md</t>
-        </is>
+      <c r="A7" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>DL-05</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Fan-out between tasks</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Valkey pub/sub on ElastiCache</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-005-fan-out-between-tasks.md</t>
-        </is>
+      <c r="A8" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>DL-06</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ID token verification</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>In code for HTTP and WebSockets</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-006-token-verification.md</t>
-        </is>
+      <c r="A9" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>DL-07</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Repository and stack layout</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Monorepo; one CDK stack per deployable; one ECS service per HTTP domain; no CloudFormation exports</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-007-stack-layout.md</t>
-        </is>
+      <c r="A10" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>DL-08</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Cross-domain reads</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Direct read of another domain's records under a stated rule; no service-to-service calls in the MVP</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>docs/adr/adr-008-cross-domain-reads.md</t>
-        </is>
+      <c r="A11" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -7013,32 +7013,112 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DL-09</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Data store</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Aurora PostgreSQL Serverless v2; one table per entity; row-level security for pond and membership</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-009-data-store.md</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>DL-10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Identity provider</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Google Sign-In, OpenID Connect ID token; no hosted user pool</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-010-identity-provider.md</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>DL-11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Initial runtime dependencies</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>drizzle-orm and drizzle-kit, pg, iovalkey, jose, fastify, zod, ws, React with Vite</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-011-initial-runtime-dependencies.md</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>DL-12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MVP scope cuts</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>OOS-01 to OOS-11 and hosted user pools out of scope; each row names what adding it changes</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>docs/adr/adr-012-mvp-scope-cuts.md</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -1706,7 +1706,7 @@
     <t>A user belongs to a flock</t>
   </si>
   <si>
-    <t>pondId, flockId, duckId, addedBy, addedAt</t>
+    <t>pondId, flockId, duckId, addedBy, createdAt</t>
   </si>
   <si>
     <t>DE-04</t>

--- a/docs/discovery/Design Playbook - Quack.xlsx
+++ b/docs/discovery/Design Playbook - Quack.xlsx
@@ -1073,7 +1073,7 @@
     <t>CON-05</t>
   </si>
   <si>
-    <t>Timebox 2026-09-12 to 2026-09-13</t>
+    <t>Initial estimate: one weekend, 2026-09-12 to 2026-09-13</t>
   </si>
   <si>
     <t>MVP only; cuts named in PLAN.md</t>
@@ -1418,7 +1418,7 @@
     <t>No audit in demo. See OOS-11.</t>
   </si>
   <si>
-    <t>2026-09-13, end of the weekend timebox. Fixed by constraint CON-01. The demo then runs one month.</t>
+    <t>2026-09-13, end of the initial one-weekend estimate (CON-01). The demo then runs one month.</t>
   </si>
   <si>
     <t>Best effort</t>
